--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BDF176-E0B0-4138-A60C-0E4600680321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C568374C-E7AA-4D53-A5DE-F40EEB75609F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="171">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -506,6 +506,74 @@
   </si>
   <si>
     <t>전체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손견</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순욱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손책</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태사자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제갈량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조운</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곽가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미부인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황충</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -513,7 +581,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -541,6 +609,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -586,7 +661,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -625,6 +700,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1021,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1FA765-18DF-4AAD-91B0-AAB6166EA35D}">
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -1029,19 +1107,20 @@
     <col min="3" max="3" width="12.25" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>76</v>
       </c>
@@ -1058,37 +1137,40 @@
         <v>36</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1105,37 +1187,40 @@
         <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>37</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>1</v>
-      </c>
       <c r="N2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1152,24 +1237,25 @@
       <c r="E3" s="2">
         <v>184</v>
       </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
         <v>10</v>
       </c>
-      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="2">
-        <v>1</v>
-      </c>
-      <c r="O3" s="6"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N3" s="4"/>
+      <c r="O3" s="2">
+        <v>1</v>
+      </c>
+      <c r="P3" s="6"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1186,30 +1272,33 @@
       <c r="E4" s="2">
         <v>184</v>
       </c>
-      <c r="F4" s="2">
-        <v>1</v>
+      <c r="F4" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
         <v>10</v>
       </c>
-      <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="4"/>
+      <c r="K4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="2">
-        <v>1</v>
-      </c>
+      <c r="M4" s="4"/>
       <c r="N4" s="2">
-        <v>2</v>
-      </c>
-      <c r="O4" s="6"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2">
+        <v>2</v>
+      </c>
+      <c r="P4" s="6"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1226,24 +1315,25 @@
       <c r="E5" s="2">
         <v>190</v>
       </c>
-      <c r="F5" s="2">
-        <v>2</v>
-      </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="2">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2">
         <v>5</v>
       </c>
-      <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="2">
+      <c r="N5" s="4"/>
+      <c r="O5" s="2">
         <v>3</v>
       </c>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1260,30 +1350,33 @@
       <c r="E6" s="2">
         <v>191</v>
       </c>
-      <c r="F6" s="2">
-        <v>2</v>
+      <c r="F6" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="G6" s="2">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2">
         <v>10</v>
       </c>
-      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="4"/>
+      <c r="K6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="2">
-        <v>1</v>
-      </c>
+      <c r="M6" s="4"/>
       <c r="N6" s="2">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2">
         <v>4</v>
       </c>
-      <c r="O6" s="6"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1300,30 +1393,33 @@
       <c r="E7" s="2">
         <v>191</v>
       </c>
-      <c r="F7" s="2">
-        <v>2</v>
+      <c r="F7" s="13" t="s">
+        <v>157</v>
       </c>
       <c r="G7" s="2">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2">
         <v>10</v>
       </c>
-      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="4"/>
+      <c r="K7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="2">
-        <v>1</v>
-      </c>
+      <c r="M7" s="4"/>
       <c r="N7" s="2">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2">
         <v>5</v>
       </c>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1340,24 +1436,27 @@
       <c r="E8" s="2">
         <v>193</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G8" s="2">
         <v>3</v>
       </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="2">
+      <c r="N8" s="4"/>
+      <c r="O8" s="2">
         <v>6</v>
       </c>
-      <c r="O8" s="6"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1374,28 +1473,31 @@
       <c r="E9" s="2">
         <v>193</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="2">
         <v>3</v>
       </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4"/>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="4"/>
+      <c r="K9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="4"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="2">
+      <c r="N9" s="4"/>
+      <c r="O9" s="2">
         <v>7</v>
       </c>
-      <c r="O9" s="6"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1412,24 +1514,27 @@
       <c r="E10" s="2">
         <v>194</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G10" s="2">
         <v>4</v>
       </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="2">
+      <c r="N10" s="4"/>
+      <c r="O10" s="2">
         <v>8</v>
       </c>
-      <c r="O10" s="6"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1446,30 +1551,33 @@
       <c r="E11" s="2">
         <v>194</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G11" s="2">
         <v>4</v>
       </c>
-      <c r="G11" s="2">
+      <c r="H11" s="2">
         <v>5</v>
       </c>
-      <c r="H11" s="4"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="4"/>
+      <c r="K11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
+      <c r="M11" s="4"/>
       <c r="N11" s="2">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2">
         <v>9</v>
       </c>
-      <c r="O11" s="6"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1486,30 +1594,33 @@
       <c r="E12" s="2">
         <v>195</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <v>5</v>
       </c>
-      <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="4"/>
+      <c r="K12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="2">
-        <v>1</v>
-      </c>
+      <c r="M12" s="4"/>
       <c r="N12" s="2">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2">
         <v>10</v>
       </c>
-      <c r="O12" s="6"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1526,24 +1637,27 @@
       <c r="E13" s="2">
         <v>196</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="2">
         <v>4</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13" s="2">
         <v>5</v>
       </c>
-      <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
-      <c r="N13" s="2">
+      <c r="N13" s="4"/>
+      <c r="O13" s="2">
         <v>11</v>
       </c>
-      <c r="O13" s="6"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1560,24 +1674,27 @@
       <c r="E14" s="2">
         <v>196</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" s="2">
         <v>4</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="2">
         <v>5</v>
       </c>
-      <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="2">
+      <c r="N14" s="4"/>
+      <c r="O14" s="2">
         <v>12</v>
       </c>
-      <c r="O14" s="6"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1594,32 +1711,35 @@
       <c r="E15" s="2">
         <v>196</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G15" s="2">
         <v>4</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="2">
         <v>5</v>
       </c>
-      <c r="H15" s="2">
-        <v>1</v>
-      </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="2" t="s">
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4"/>
+      <c r="K15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L15" s="2">
-        <v>2</v>
-      </c>
-      <c r="M15" s="4"/>
-      <c r="N15" s="2">
+      <c r="M15" s="2">
+        <v>2</v>
+      </c>
+      <c r="N15" s="4"/>
+      <c r="O15" s="2">
         <v>12</v>
       </c>
-      <c r="O15" s="6"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1636,30 +1756,31 @@
       <c r="E16" s="2">
         <v>199</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2">
         <v>6</v>
       </c>
-      <c r="G16" s="2">
+      <c r="H16" s="2">
         <v>10</v>
       </c>
-      <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="4"/>
+      <c r="K16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="2">
-        <v>1</v>
-      </c>
+      <c r="M16" s="4"/>
       <c r="N16" s="2">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2">
         <v>13</v>
       </c>
-      <c r="O16" s="6"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1676,24 +1797,27 @@
       <c r="E17" s="2">
         <v>199</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="G17" s="2">
         <v>7</v>
       </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4"/>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="2">
+      <c r="N17" s="4"/>
+      <c r="O17" s="2">
         <v>14</v>
       </c>
-      <c r="O17" s="6"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -1710,26 +1834,29 @@
       <c r="E18" s="2">
         <v>200</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="G18" s="2">
         <v>7</v>
       </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
       <c r="H18" s="2">
         <v>1</v>
       </c>
-      <c r="I18" s="4"/>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="2">
+      <c r="N18" s="4"/>
+      <c r="O18" s="2">
         <v>15</v>
       </c>
-      <c r="O18" s="6"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -1746,28 +1873,31 @@
       <c r="E19" s="2">
         <v>200</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="G19" s="2">
         <v>7</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19" s="2">
         <v>5</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="2">
-        <v>2</v>
-      </c>
-      <c r="J19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="2">
+        <v>2</v>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="2">
+      <c r="N19" s="4"/>
+      <c r="O19" s="2">
         <v>16</v>
       </c>
-      <c r="O19" s="6" t="s">
+      <c r="P19" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -1784,30 +1914,33 @@
       <c r="E20" s="2">
         <v>200</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G20" s="2">
         <v>7</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="2">
         <v>5</v>
       </c>
-      <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="4"/>
+      <c r="K20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="2">
-        <v>1</v>
-      </c>
+      <c r="M20" s="4"/>
       <c r="N20" s="2">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2">
         <v>17</v>
       </c>
-      <c r="O20" s="6"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1824,30 +1957,33 @@
       <c r="E21" s="2">
         <v>200</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G21" s="2">
         <v>7</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21" s="2">
         <v>5</v>
       </c>
-      <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="4"/>
+      <c r="K21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L21" s="4"/>
-      <c r="M21" s="2">
-        <v>1</v>
-      </c>
+      <c r="M21" s="4"/>
       <c r="N21" s="2">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2">
         <v>18</v>
       </c>
-      <c r="O21" s="6"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -1864,24 +2000,27 @@
       <c r="E22" s="2">
         <v>207</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G22" s="2">
         <v>7</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <v>10</v>
       </c>
-      <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="2">
+      <c r="N22" s="4"/>
+      <c r="O22" s="2">
         <v>19</v>
       </c>
-      <c r="O22" s="6"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -1898,32 +2037,35 @@
       <c r="E23" s="2">
         <v>207</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="G23" s="2">
         <v>7</v>
       </c>
-      <c r="G23" s="2">
+      <c r="H23" s="2">
         <v>10</v>
       </c>
-      <c r="H23" s="2">
-        <v>1</v>
-      </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="2" t="s">
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="4"/>
+      <c r="K23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="L23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L23" s="2">
-        <v>2</v>
-      </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="2">
+      <c r="M23" s="2">
+        <v>2</v>
+      </c>
+      <c r="N23" s="4"/>
+      <c r="O23" s="2">
         <v>19</v>
       </c>
-      <c r="O23" s="6"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P23" s="6"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
@@ -1940,30 +2082,33 @@
       <c r="E24" s="2">
         <v>207</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="2">
         <v>8</v>
       </c>
-      <c r="G24" s="2">
+      <c r="H24" s="2">
         <v>5</v>
       </c>
-      <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="4"/>
+      <c r="K24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="L24" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="2">
-        <v>1</v>
-      </c>
+      <c r="M24" s="4"/>
       <c r="N24" s="2">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2">
         <v>20</v>
       </c>
-      <c r="O24" s="6"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P24" s="6"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -1980,24 +2125,27 @@
       <c r="E25" s="2">
         <v>208</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G25" s="2">
         <v>9</v>
       </c>
-      <c r="G25" s="2">
+      <c r="H25" s="2">
         <v>5</v>
       </c>
-      <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="2">
+      <c r="N25" s="4"/>
+      <c r="O25" s="2">
         <v>21</v>
       </c>
-      <c r="O25" s="6"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P25" s="6"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
@@ -2014,26 +2162,29 @@
       <c r="E26" s="2">
         <v>208</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G26" s="2">
         <v>9</v>
       </c>
-      <c r="G26" s="2">
+      <c r="H26" s="2">
         <v>5</v>
       </c>
-      <c r="H26" s="2">
-        <v>1</v>
-      </c>
-      <c r="I26" s="4"/>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
-      <c r="N26" s="2">
+      <c r="N26" s="4"/>
+      <c r="O26" s="2">
         <v>21</v>
       </c>
-      <c r="O26" s="6"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P26" s="6"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -2050,30 +2201,33 @@
       <c r="E27" s="2">
         <v>208</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="G27" s="2">
         <v>9</v>
       </c>
-      <c r="G27" s="2">
+      <c r="H27" s="2">
         <v>10</v>
       </c>
-      <c r="H27" s="2">
-        <v>1</v>
-      </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="2" t="s">
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="K27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L27" s="4"/>
       <c r="M27" s="4"/>
-      <c r="N27" s="2">
+      <c r="N27" s="4"/>
+      <c r="O27" s="2">
         <v>22</v>
       </c>
-      <c r="O27" s="6"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
@@ -2090,24 +2244,27 @@
       <c r="E28" s="2">
         <v>208</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G28" s="2">
         <v>10</v>
       </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="4"/>
+      <c r="H28" s="2">
+        <v>1</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
-      <c r="N28" s="2">
+      <c r="N28" s="4"/>
+      <c r="O28" s="2">
         <v>23</v>
       </c>
-      <c r="O28" s="6"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -2124,26 +2281,29 @@
       <c r="E29" s="2">
         <v>208</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G29" s="2">
         <v>10</v>
       </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
       <c r="H29" s="2">
         <v>1</v>
       </c>
-      <c r="I29" s="4"/>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
-      <c r="N29" s="2">
+      <c r="N29" s="4"/>
+      <c r="O29" s="2">
         <v>23</v>
       </c>
-      <c r="O29" s="6"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P29" s="6"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
@@ -2160,24 +2320,27 @@
       <c r="E30" s="2">
         <v>208</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="G30" s="2">
         <v>10</v>
       </c>
-      <c r="G30" s="2">
+      <c r="H30" s="2">
         <v>5</v>
       </c>
-      <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
-      <c r="N30" s="2">
+      <c r="N30" s="4"/>
+      <c r="O30" s="2">
         <v>24</v>
       </c>
-      <c r="O30" s="6"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P30" s="6"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -2185,35 +2348,38 @@
         <v>95</v>
       </c>
       <c r="C31" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2" t="str">
         <f>VLOOKUP(C31,Overview!$B$2:$C$6,2,FALSE)</f>
-        <v>오</v>
+        <v>위</v>
       </c>
       <c r="E31" s="2">
         <v>208</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G31" s="2">
         <v>10</v>
       </c>
-      <c r="G31" s="2">
+      <c r="H31" s="2">
         <v>5</v>
       </c>
-      <c r="H31" s="2">
-        <v>1</v>
-      </c>
-      <c r="I31" s="4"/>
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
-      <c r="N31" s="2">
+      <c r="N31" s="4"/>
+      <c r="O31" s="2">
         <v>24</v>
       </c>
-      <c r="O31" s="6"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P31" s="6"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
@@ -2230,24 +2396,27 @@
       <c r="E32" s="2">
         <v>208</v>
       </c>
-      <c r="F32" s="2">
-        <v>10</v>
+      <c r="F32" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="G32" s="2">
         <v>10</v>
       </c>
-      <c r="H32" s="4"/>
+      <c r="H32" s="2">
+        <v>10</v>
+      </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
-      <c r="N32" s="2">
+      <c r="N32" s="4"/>
+      <c r="O32" s="2">
         <v>25</v>
       </c>
-      <c r="O32" s="6"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -2264,30 +2433,33 @@
       <c r="E33" s="2">
         <v>209</v>
       </c>
-      <c r="F33" s="2">
-        <v>10</v>
+      <c r="F33" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="G33" s="2">
         <v>10</v>
       </c>
-      <c r="H33" s="4"/>
+      <c r="H33" s="2">
+        <v>10</v>
+      </c>
       <c r="I33" s="4"/>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="4"/>
+      <c r="K33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="2">
-        <v>1</v>
-      </c>
+      <c r="M33" s="4"/>
       <c r="N33" s="2">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2">
         <v>26</v>
       </c>
-      <c r="O33" s="6"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P33" s="6"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
@@ -2304,7 +2476,9 @@
       <c r="E34" s="2">
         <v>200</v>
       </c>
-      <c r="F34" s="4"/>
+      <c r="F34" s="13" t="s">
+        <v>164</v>
+      </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
@@ -2312,14 +2486,15 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
-      <c r="N34" s="2">
-        <v>1</v>
-      </c>
-      <c r="O34" s="6" t="s">
+      <c r="N34" s="4"/>
+      <c r="O34" s="2">
+        <v>1</v>
+      </c>
+      <c r="P34" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
@@ -2336,7 +2511,9 @@
       <c r="E35" s="2">
         <v>200</v>
       </c>
-      <c r="F35" s="4"/>
+      <c r="F35" s="13" t="s">
+        <v>164</v>
+      </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -2344,14 +2521,15 @@
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="2">
-        <v>2</v>
-      </c>
-      <c r="O35" s="6" t="s">
+      <c r="N35" s="4"/>
+      <c r="O35" s="2">
+        <v>2</v>
+      </c>
+      <c r="P35" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
@@ -2368,7 +2546,9 @@
       <c r="E36" s="2">
         <v>200</v>
       </c>
-      <c r="F36" s="4"/>
+      <c r="F36" s="13" t="s">
+        <v>164</v>
+      </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -2376,10 +2556,11 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="2">
+      <c r="N36" s="4"/>
+      <c r="O36" s="2">
         <v>3</v>
       </c>
-      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C568374C-E7AA-4D53-A5DE-F40EEB75609F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9025E440-EAF3-4887-B6F4-DE5395AF0285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="172">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -574,6 +574,10 @@
   </si>
   <si>
     <t>황충</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1099,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1FA765-18DF-4AAD-91B0-AAB6166EA35D}">
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -1108,19 +1112,20 @@
     <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.5" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>76</v>
       </c>
@@ -1140,37 +1145,43 @@
         <v>154</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1196,31 +1207,37 @@
         <v>37</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="K2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>1</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1244,18 +1261,24 @@
       <c r="H3" s="2">
         <v>10</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="2">
-        <v>1</v>
-      </c>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="2">
+        <v>1</v>
+      </c>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1281,24 +1304,31 @@
       <c r="H4" s="2">
         <v>10</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="2" t="s">
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <f>J3+1</f>
+        <v>2</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="2">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2">
-        <v>2</v>
-      </c>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O4" s="4"/>
+      <c r="P4" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>2</v>
+      </c>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1322,18 +1352,25 @@
       <c r="H5" s="2">
         <v>5</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <f>J4+1</f>
+        <v>3</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="2">
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="2">
         <v>3</v>
       </c>
-      <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1359,24 +1396,31 @@
       <c r="H6" s="2">
         <v>10</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="2" t="s">
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <f>J5+1</f>
+        <v>4</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="2">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2">
+      <c r="O6" s="4"/>
+      <c r="P6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2">
         <v>4</v>
       </c>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R6" s="6"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1402,24 +1446,31 @@
       <c r="H7" s="2">
         <v>10</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="2" t="s">
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <f>J6+1</f>
+        <v>5</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="2">
-        <v>1</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="O7" s="4"/>
+      <c r="P7" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2">
         <v>5</v>
       </c>
-      <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R7" s="6"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1445,18 +1496,25 @@
       <c r="H8" s="2">
         <v>1</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <f>J7+1</f>
+        <v>6</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="2">
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="2">
         <v>6</v>
       </c>
-      <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R8" s="6"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1482,22 +1540,29 @@
       <c r="H9" s="2">
         <v>1</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="2" t="s">
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <f>J8+1</f>
+        <v>7</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="2">
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="2">
         <v>7</v>
       </c>
-      <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R9" s="6"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1523,18 +1588,25 @@
       <c r="H10" s="2">
         <v>1</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <f>J9+1</f>
+        <v>8</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="2">
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="2">
         <v>8</v>
       </c>
-      <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R10" s="6"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1560,24 +1632,31 @@
       <c r="H11" s="2">
         <v>5</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="2" t="s">
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <f>J10+1</f>
+        <v>9</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="2">
-        <v>1</v>
-      </c>
-      <c r="O11" s="2">
+      <c r="O11" s="4"/>
+      <c r="P11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="2">
         <v>9</v>
       </c>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R11" s="6"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1603,24 +1682,31 @@
       <c r="H12" s="2">
         <v>5</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="2" t="s">
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <f>J11+1</f>
+        <v>10</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="2">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2">
+      <c r="O12" s="4"/>
+      <c r="P12" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="2">
         <v>10</v>
       </c>
-      <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1646,18 +1732,24 @@
       <c r="H13" s="2">
         <v>5</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="2">
+        <v>2</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="2">
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="2">
         <v>11</v>
       </c>
-      <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1683,18 +1775,25 @@
       <c r="H14" s="2">
         <v>5</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="I14" s="2">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
+        <f>J13+1</f>
+        <v>2</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
-      <c r="O14" s="2">
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="2">
         <v>12</v>
       </c>
-      <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R14" s="6"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1721,25 +1820,32 @@
         <v>5</v>
       </c>
       <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2">
+        <f>J14+1</f>
+        <v>3</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4"/>
+      <c r="M15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="M15" s="2">
-        <v>2</v>
-      </c>
-      <c r="N15" s="4"/>
       <c r="O15" s="2">
+        <v>2</v>
+      </c>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="2">
         <v>12</v>
       </c>
-      <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R15" s="6"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1763,24 +1869,31 @@
       <c r="H16" s="2">
         <v>10</v>
       </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="2" t="s">
+      <c r="I16" s="2">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
+        <f>J15+1</f>
+        <v>4</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="M16" s="4"/>
-      <c r="N16" s="2">
-        <v>1</v>
-      </c>
-      <c r="O16" s="2">
+      <c r="O16" s="4"/>
+      <c r="P16" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2">
         <v>13</v>
       </c>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R16" s="6"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1806,18 +1919,25 @@
       <c r="H17" s="2">
         <v>1</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="I17" s="2">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
+        <f>J16+1</f>
+        <v>5</v>
+      </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
-      <c r="O17" s="2">
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="2">
         <v>14</v>
       </c>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R17" s="6"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -1844,19 +1964,26 @@
         <v>1</v>
       </c>
       <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="J18" s="2">
+        <f>J17+1</f>
+        <v>6</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
-      <c r="O18" s="2">
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="2">
         <v>15</v>
       </c>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R18" s="6"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -1882,22 +2009,29 @@
       <c r="H19" s="2">
         <v>5</v>
       </c>
-      <c r="I19" s="4"/>
+      <c r="I19" s="2">
+        <v>2</v>
+      </c>
       <c r="J19" s="2">
-        <v>2</v>
+        <f>J18+1</f>
+        <v>7</v>
       </c>
       <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
+      <c r="L19" s="2">
+        <v>2</v>
+      </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
-      <c r="O19" s="2">
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="2">
         <v>16</v>
       </c>
-      <c r="P19" s="6" t="s">
+      <c r="R19" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -1923,24 +2057,31 @@
       <c r="H20" s="2">
         <v>5</v>
       </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="2" t="s">
+      <c r="I20" s="2">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2">
+        <f>J19+1</f>
+        <v>8</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="2">
-        <v>1</v>
-      </c>
-      <c r="O20" s="2">
+      <c r="O20" s="4"/>
+      <c r="P20" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="2">
         <v>17</v>
       </c>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R20" s="6"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1966,24 +2107,31 @@
       <c r="H21" s="2">
         <v>5</v>
       </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="2" t="s">
+      <c r="I21" s="2">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2">
+        <f>J20+1</f>
+        <v>9</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M21" s="4"/>
-      <c r="N21" s="2">
-        <v>1</v>
-      </c>
-      <c r="O21" s="2">
+      <c r="O21" s="4"/>
+      <c r="P21" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="2">
         <v>18</v>
       </c>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R21" s="6"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -2009,18 +2157,25 @@
       <c r="H22" s="2">
         <v>10</v>
       </c>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="I22" s="2">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2">
+        <f>J21+1</f>
+        <v>10</v>
+      </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
-      <c r="O22" s="2">
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="2">
         <v>19</v>
       </c>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R22" s="6"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -2047,25 +2202,31 @@
         <v>10</v>
       </c>
       <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="4"/>
+      <c r="M23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M23" s="2">
-        <v>2</v>
-      </c>
-      <c r="N23" s="4"/>
       <c r="O23" s="2">
+        <v>2</v>
+      </c>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="2">
         <v>19</v>
       </c>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R23" s="6"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
@@ -2091,24 +2252,31 @@
       <c r="H24" s="2">
         <v>5</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="2" t="s">
+      <c r="I24" s="2">
+        <v>3</v>
+      </c>
+      <c r="J24" s="2">
+        <f>J23+1</f>
+        <v>2</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M24" s="4"/>
-      <c r="N24" s="2">
-        <v>1</v>
-      </c>
-      <c r="O24" s="2">
+      <c r="O24" s="4"/>
+      <c r="P24" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2">
         <v>20</v>
       </c>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R24" s="6"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -2134,18 +2302,25 @@
       <c r="H25" s="2">
         <v>5</v>
       </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="I25" s="2">
+        <v>3</v>
+      </c>
+      <c r="J25" s="2">
+        <f>J24+1</f>
+        <v>3</v>
+      </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
-      <c r="O25" s="2">
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="2">
         <v>21</v>
       </c>
-      <c r="P25" s="6"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R25" s="6"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
@@ -2172,19 +2347,26 @@
         <v>5</v>
       </c>
       <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="J26" s="2">
+        <f>J25+1</f>
+        <v>4</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
-      <c r="O26" s="2">
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="2">
         <v>21</v>
       </c>
-      <c r="P26" s="6"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R26" s="6"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -2211,23 +2393,30 @@
         <v>10</v>
       </c>
       <c r="I27" s="2">
-        <v>1</v>
-      </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="2">
+        <f>J26+1</f>
+        <v>5</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="4"/>
+      <c r="M27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="2">
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="2">
         <v>22</v>
       </c>
-      <c r="P27" s="6"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R27" s="6"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
@@ -2253,18 +2442,25 @@
       <c r="H28" s="2">
         <v>1</v>
       </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="I28" s="2">
+        <v>3</v>
+      </c>
+      <c r="J28" s="2">
+        <f>J27+1</f>
+        <v>6</v>
+      </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
-      <c r="O28" s="2">
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="2">
         <v>23</v>
       </c>
-      <c r="P28" s="6"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R28" s="6"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -2291,19 +2487,26 @@
         <v>1</v>
       </c>
       <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="J29" s="2">
+        <f>J28+1</f>
+        <v>7</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
-      <c r="O29" s="2">
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="2">
         <v>23</v>
       </c>
-      <c r="P29" s="6"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R29" s="6"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
@@ -2329,18 +2532,25 @@
       <c r="H30" s="2">
         <v>5</v>
       </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
+      <c r="I30" s="2">
+        <v>3</v>
+      </c>
+      <c r="J30" s="2">
+        <f>J29+1</f>
+        <v>8</v>
+      </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-      <c r="O30" s="2">
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="2">
         <v>24</v>
       </c>
-      <c r="P30" s="6"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R30" s="6"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -2367,19 +2577,26 @@
         <v>5</v>
       </c>
       <c r="I31" s="2">
-        <v>1</v>
-      </c>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="J31" s="2">
+        <f>J30+1</f>
+        <v>9</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="2">
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="2">
         <v>24</v>
       </c>
-      <c r="P31" s="6"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R31" s="6"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
@@ -2405,18 +2622,25 @@
       <c r="H32" s="2">
         <v>10</v>
       </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
+      <c r="I32" s="2">
+        <v>3</v>
+      </c>
+      <c r="J32" s="2">
+        <f>J31+1</f>
+        <v>10</v>
+      </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
-      <c r="O32" s="2">
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="2">
         <v>25</v>
       </c>
-      <c r="P32" s="6"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R32" s="6"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -2442,24 +2666,30 @@
       <c r="H33" s="2">
         <v>10</v>
       </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="2" t="s">
+      <c r="I33" s="2">
+        <v>4</v>
+      </c>
+      <c r="J33" s="2">
+        <v>1</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M33" s="4"/>
-      <c r="N33" s="2">
-        <v>1</v>
-      </c>
-      <c r="O33" s="2">
+      <c r="O33" s="4"/>
+      <c r="P33" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="2">
         <v>26</v>
       </c>
-      <c r="P33" s="6"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R33" s="6"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
@@ -2479,22 +2709,24 @@
       <c r="F34" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-      <c r="O34" s="2">
-        <v>1</v>
-      </c>
-      <c r="P34" s="6" t="s">
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="2">
+        <v>1</v>
+      </c>
+      <c r="R34" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
@@ -2514,22 +2746,24 @@
       <c r="F35" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-      <c r="O35" s="2">
-        <v>2</v>
-      </c>
-      <c r="P35" s="6" t="s">
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="2">
+        <v>2</v>
+      </c>
+      <c r="R35" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
@@ -2549,18 +2783,20 @@
       <c r="F36" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
-      <c r="O36" s="2">
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="2">
         <v>3</v>
       </c>
-      <c r="P36" s="6"/>
+      <c r="R36" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9025E440-EAF3-4887-B6F4-DE5395AF0285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58F0F25-CFE3-449C-A6B4-48DE3DCD4621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1308,7 +1308,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="2">
-        <f>J3+1</f>
+        <f t="shared" ref="J4:J12" si="0">J3+1</f>
         <v>2</v>
       </c>
       <c r="K4" s="4"/>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="2">
-        <f>J4+1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="K5" s="4"/>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="2">
-        <f>J5+1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="K6" s="4"/>
@@ -1450,7 +1450,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="2">
-        <f>J6+1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="K7" s="4"/>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="2">
-        <f>J7+1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="K8" s="4"/>
@@ -1544,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="2">
-        <f>J8+1</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="K9" s="4"/>
@@ -1592,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="2">
-        <f>J9+1</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="K10" s="4"/>
@@ -1636,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="2">
-        <f>J10+1</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="K11" s="4"/>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="2">
-        <f>J11+1</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="K12" s="4"/>
@@ -1779,7 +1779,7 @@
         <v>2</v>
       </c>
       <c r="J14" s="2">
-        <f>J13+1</f>
+        <f t="shared" ref="J14:J22" si="1">J13+1</f>
         <v>2</v>
       </c>
       <c r="K14" s="4"/>
@@ -1823,8 +1823,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="2">
-        <f>J14+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
@@ -1873,8 +1872,8 @@
         <v>2</v>
       </c>
       <c r="J16" s="2">
-        <f>J15+1</f>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1923,8 +1922,8 @@
         <v>2</v>
       </c>
       <c r="J17" s="2">
-        <f>J16+1</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1967,8 +1966,8 @@
         <v>2</v>
       </c>
       <c r="J18" s="2">
-        <f>J17+1</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="K18" s="2">
         <v>1</v>
@@ -2013,8 +2012,8 @@
         <v>2</v>
       </c>
       <c r="J19" s="2">
-        <f>J18+1</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="2">
@@ -2061,8 +2060,8 @@
         <v>2</v>
       </c>
       <c r="J20" s="2">
-        <f>J19+1</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -2111,8 +2110,8 @@
         <v>2</v>
       </c>
       <c r="J21" s="2">
-        <f>J20+1</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -2161,8 +2160,8 @@
         <v>2</v>
       </c>
       <c r="J22" s="2">
-        <f>J21+1</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -2202,10 +2201,10 @@
         <v>10</v>
       </c>
       <c r="I23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K23" s="2">
         <v>1</v>
@@ -2256,8 +2255,7 @@
         <v>3</v>
       </c>
       <c r="J24" s="2">
-        <f>J23+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -2306,8 +2304,8 @@
         <v>3</v>
       </c>
       <c r="J25" s="2">
-        <f>J24+1</f>
-        <v>3</v>
+        <f t="shared" ref="J25:J32" si="2">J24+1</f>
+        <v>2</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -2350,8 +2348,7 @@
         <v>3</v>
       </c>
       <c r="J26" s="2">
-        <f>J25+1</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K26" s="2">
         <v>1</v>
@@ -2396,8 +2393,8 @@
         <v>3</v>
       </c>
       <c r="J27" s="2">
-        <f>J26+1</f>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
@@ -2446,8 +2443,8 @@
         <v>3</v>
       </c>
       <c r="J28" s="2">
-        <f>J27+1</f>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -2490,8 +2487,7 @@
         <v>3</v>
       </c>
       <c r="J29" s="2">
-        <f>J28+1</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K29" s="2">
         <v>1</v>
@@ -2536,8 +2532,8 @@
         <v>3</v>
       </c>
       <c r="J30" s="2">
-        <f>J29+1</f>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -2580,8 +2576,7 @@
         <v>3</v>
       </c>
       <c r="J31" s="2">
-        <f>J30+1</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
@@ -2626,8 +2621,8 @@
         <v>3</v>
       </c>
       <c r="J32" s="2">
-        <f>J31+1</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -2667,10 +2662,10 @@
         <v>10</v>
       </c>
       <c r="I33" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58F0F25-CFE3-449C-A6B4-48DE3DCD4621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C097AD7C-DF89-4D43-A861-2AF5162B7FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2022,7 +2022,9 @@
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
+      <c r="P19" s="4">
+        <v>1</v>
+      </c>
       <c r="Q19" s="2">
         <v>16</v>
       </c>

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C097AD7C-DF89-4D43-A861-2AF5162B7FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2F19E0-9430-43A8-A23D-4AFEC648C6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="175">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -579,13 +579,22 @@
   <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_currency_type</t>
+  </si>
+  <si>
+    <t>reward_currency_amount</t>
+  </si>
+  <si>
+    <t>gold</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -621,6 +630,13 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -636,7 +652,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -659,13 +675,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -707,6 +736,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1103,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1FA765-18DF-4AAD-91B0-AAB6166EA35D}">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -1117,15 +1158,17 @@
     <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.125" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.375" style="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.5" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>76</v>
       </c>
@@ -1162,26 +1205,32 @@
       <c r="L1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1218,26 +1267,32 @@
       <c r="L2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>1</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1268,17 +1323,23 @@
         <v>1</v>
       </c>
       <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="N3" s="16">
+        <v>500</v>
+      </c>
+      <c r="O3" s="14"/>
       <c r="P3" s="4"/>
-      <c r="Q3" s="2">
-        <v>1</v>
-      </c>
-      <c r="R3" s="6"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q3" s="4"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2">
+        <v>1</v>
+      </c>
+      <c r="T3" s="6"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1313,22 +1374,24 @@
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>2</v>
-      </c>
-      <c r="R4" s="6"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q4" s="4"/>
+      <c r="R4" s="2">
+        <v>1</v>
+      </c>
+      <c r="S4" s="2">
+        <v>2</v>
+      </c>
+      <c r="T4" s="6"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1361,16 +1424,22 @@
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
+      <c r="M5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N5" s="2">
+        <v>500</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
-      <c r="Q5" s="2">
+      <c r="Q5" s="4"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2">
         <v>3</v>
       </c>
-      <c r="R5" s="6"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T5" s="6"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1405,22 +1474,24 @@
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="4"/>
+      <c r="R6" s="2">
+        <v>1</v>
+      </c>
+      <c r="S6" s="2">
         <v>4</v>
       </c>
-      <c r="R6" s="6"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T6" s="6"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1455,22 +1526,24 @@
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="4"/>
+      <c r="R7" s="2">
+        <v>1</v>
+      </c>
+      <c r="S7" s="2">
         <v>5</v>
       </c>
-      <c r="R7" s="6"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T7" s="6"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1505,16 +1578,22 @@
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
+      <c r="M8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N8" s="2">
+        <v>500</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="2">
+      <c r="Q8" s="4"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2">
         <v>6</v>
       </c>
-      <c r="R8" s="6"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T8" s="6"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1549,20 +1628,22 @@
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="2">
+      <c r="Q9" s="4"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2">
         <v>7</v>
       </c>
-      <c r="R9" s="6"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T9" s="6"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1597,16 +1678,22 @@
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+      <c r="M10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N10" s="2">
+        <v>500</v>
+      </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
-      <c r="Q10" s="2">
+      <c r="Q10" s="4"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2">
         <v>8</v>
       </c>
-      <c r="R10" s="6"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T10" s="6"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1641,22 +1728,24 @@
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="4"/>
+      <c r="R11" s="2">
+        <v>1</v>
+      </c>
+      <c r="S11" s="2">
         <v>9</v>
       </c>
-      <c r="R11" s="6"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T11" s="6"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1691,22 +1780,24 @@
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="O12" s="4"/>
-      <c r="P12" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="4"/>
+      <c r="R12" s="2">
+        <v>1</v>
+      </c>
+      <c r="S12" s="2">
         <v>10</v>
       </c>
-      <c r="R12" s="6"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T12" s="6"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1740,16 +1831,22 @@
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
+      <c r="M13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N13" s="2">
+        <v>500</v>
+      </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="2">
+      <c r="Q13" s="4"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2">
         <v>11</v>
       </c>
-      <c r="R13" s="6"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T13" s="6"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1784,16 +1881,22 @@
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
+      <c r="M14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N14" s="2">
+        <v>500</v>
+      </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
-      <c r="Q14" s="2">
+      <c r="Q14" s="4"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2">
         <v>12</v>
       </c>
-      <c r="R14" s="6"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T14" s="6"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1829,22 +1932,24 @@
         <v>1</v>
       </c>
       <c r="L15" s="4"/>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="O15" s="2">
-        <v>2</v>
-      </c>
-      <c r="P15" s="4"/>
       <c r="Q15" s="2">
+        <v>2</v>
+      </c>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2">
         <v>12</v>
       </c>
-      <c r="R15" s="6"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T15" s="6"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1877,22 +1982,24 @@
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="4"/>
+      <c r="R16" s="2">
+        <v>1</v>
+      </c>
+      <c r="S16" s="2">
         <v>13</v>
       </c>
-      <c r="R16" s="6"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T16" s="6"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1927,16 +2034,22 @@
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
+      <c r="M17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N17" s="2">
+        <v>500</v>
+      </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="2">
+      <c r="Q17" s="4"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2">
         <v>14</v>
       </c>
-      <c r="R17" s="6"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T17" s="6"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -1973,16 +2086,22 @@
         <v>1</v>
       </c>
       <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
+      <c r="M18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N18" s="2">
+        <v>500</v>
+      </c>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
-      <c r="Q18" s="2">
+      <c r="Q18" s="4"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2">
         <v>15</v>
       </c>
-      <c r="R18" s="6"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T18" s="6"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -2019,20 +2138,26 @@
       <c r="L19" s="2">
         <v>2</v>
       </c>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
+      <c r="M19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N19" s="2">
+        <v>500</v>
+      </c>
       <c r="O19" s="4"/>
-      <c r="P19" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="2">
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="2">
+        <v>1</v>
+      </c>
+      <c r="S19" s="2">
         <v>16</v>
       </c>
-      <c r="R19" s="6" t="s">
+      <c r="T19" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -2067,22 +2192,24 @@
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O20" s="4"/>
-      <c r="P20" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="4"/>
+      <c r="R20" s="2">
+        <v>1</v>
+      </c>
+      <c r="S20" s="2">
         <v>17</v>
       </c>
-      <c r="R20" s="6"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T20" s="6"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2117,22 +2244,24 @@
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="O21" s="4"/>
-      <c r="P21" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="4"/>
+      <c r="R21" s="2">
+        <v>1</v>
+      </c>
+      <c r="S21" s="2">
         <v>18</v>
       </c>
-      <c r="R21" s="6"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T21" s="6"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -2167,16 +2296,22 @@
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
+      <c r="M22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N22" s="2">
+        <v>500</v>
+      </c>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
-      <c r="Q22" s="2">
+      <c r="Q22" s="4"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2">
         <v>19</v>
       </c>
-      <c r="R22" s="6"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T22" s="6"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -2212,22 +2347,24 @@
         <v>1</v>
       </c>
       <c r="L23" s="4"/>
-      <c r="M23" s="2" t="s">
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="O23" s="2">
-        <v>2</v>
-      </c>
-      <c r="P23" s="4"/>
       <c r="Q23" s="2">
+        <v>2</v>
+      </c>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2">
         <v>19</v>
       </c>
-      <c r="R23" s="6"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T23" s="6"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
@@ -2261,22 +2398,24 @@
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
-      <c r="M24" s="2" t="s">
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O24" s="4"/>
-      <c r="P24" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="4"/>
+      <c r="R24" s="2">
+        <v>1</v>
+      </c>
+      <c r="S24" s="2">
         <v>20</v>
       </c>
-      <c r="R24" s="6"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T24" s="6"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -2311,16 +2450,22 @@
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
+      <c r="M25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N25" s="2">
+        <v>500</v>
+      </c>
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
-      <c r="Q25" s="2">
+      <c r="Q25" s="4"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2">
         <v>21</v>
       </c>
-      <c r="R25" s="6"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T25" s="6"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
@@ -2356,16 +2501,22 @@
         <v>1</v>
       </c>
       <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
+      <c r="M26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N26" s="2">
+        <v>500</v>
+      </c>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
-      <c r="Q26" s="2">
+      <c r="Q26" s="4"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2">
         <v>21</v>
       </c>
-      <c r="R26" s="6"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T26" s="6"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -2402,20 +2553,22 @@
         <v>1</v>
       </c>
       <c r="L27" s="4"/>
-      <c r="M27" s="2" t="s">
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="2">
+      <c r="Q27" s="4"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2">
         <v>22</v>
       </c>
-      <c r="R27" s="6"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T27" s="6"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
@@ -2450,16 +2603,22 @@
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
+      <c r="M28" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N28" s="2">
+        <v>500</v>
+      </c>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
-      <c r="Q28" s="2">
+      <c r="Q28" s="4"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2">
         <v>23</v>
       </c>
-      <c r="R28" s="6"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T28" s="6"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -2495,16 +2654,22 @@
         <v>1</v>
       </c>
       <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
+      <c r="M29" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N29" s="2">
+        <v>500</v>
+      </c>
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
-      <c r="Q29" s="2">
+      <c r="Q29" s="4"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2">
         <v>23</v>
       </c>
-      <c r="R29" s="6"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T29" s="6"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
@@ -2539,16 +2704,22 @@
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
+      <c r="M30" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N30" s="2">
+        <v>500</v>
+      </c>
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
-      <c r="Q30" s="2">
+      <c r="Q30" s="4"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2">
         <v>24</v>
       </c>
-      <c r="R30" s="6"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T30" s="6"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -2584,16 +2755,22 @@
         <v>1</v>
       </c>
       <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
+      <c r="M31" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N31" s="2">
+        <v>500</v>
+      </c>
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
-      <c r="Q31" s="2">
+      <c r="Q31" s="4"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2">
         <v>24</v>
       </c>
-      <c r="R31" s="6"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T31" s="6"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
@@ -2628,16 +2805,22 @@
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
+      <c r="M32" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N32" s="2">
+        <v>500</v>
+      </c>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
-      <c r="Q32" s="2">
+      <c r="Q32" s="4"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2">
         <v>25</v>
       </c>
-      <c r="R32" s="6"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T32" s="6"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -2671,22 +2854,24 @@
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
-      <c r="M33" s="2" t="s">
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="P33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="O33" s="4"/>
-      <c r="P33" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="4"/>
+      <c r="R33" s="2">
+        <v>1</v>
+      </c>
+      <c r="S33" s="2">
         <v>26</v>
       </c>
-      <c r="R33" s="6"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="T33" s="6"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
@@ -2712,18 +2897,26 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
+      <c r="M34" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N34" s="2">
+        <v>500</v>
+      </c>
       <c r="O34" s="4"/>
       <c r="P34" s="4"/>
-      <c r="Q34" s="2">
-        <v>1</v>
-      </c>
-      <c r="R34" s="6" t="s">
+      <c r="Q34" s="4"/>
+      <c r="R34" s="2">
+        <v>1</v>
+      </c>
+      <c r="S34" s="2">
+        <v>1</v>
+      </c>
+      <c r="T34" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
@@ -2749,18 +2942,26 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
+      <c r="M35" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N35" s="2">
+        <v>500</v>
+      </c>
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
-      <c r="Q35" s="2">
-        <v>2</v>
-      </c>
-      <c r="R35" s="6" t="s">
+      <c r="Q35" s="4"/>
+      <c r="R35" s="2">
+        <v>1</v>
+      </c>
+      <c r="S35" s="2">
+        <v>2</v>
+      </c>
+      <c r="T35" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
@@ -2786,14 +2987,22 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
+      <c r="M36" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="N36" s="2">
+        <v>500</v>
+      </c>
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
-      <c r="Q36" s="2">
+      <c r="Q36" s="4"/>
+      <c r="R36" s="2">
+        <v>1</v>
+      </c>
+      <c r="S36" s="2">
         <v>3</v>
       </c>
-      <c r="R36" s="6"/>
+      <c r="T36" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42CBFB5-7F8E-45B8-81B5-0A7786E4C453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7312F42D-3569-41CE-97E9-3040550C6178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2134,9 +2134,7 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="T19" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="T19" s="1"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -2295,7 +2293,9 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="T22" s="1"/>
+      <c r="T22" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -2916,9 +2916,7 @@
       <c r="S34" s="1">
         <v>25</v>
       </c>
-      <c r="T34" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="T34" s="1"/>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -2968,9 +2966,7 @@
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="T35" s="1" t="s">
-        <v>78</v>
-      </c>
+      <c r="T35" s="1"/>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -3065,7 +3061,9 @@
       <c r="S37" s="1">
         <v>1</v>
       </c>
-      <c r="T37" s="1"/>
+      <c r="T37" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -3109,7 +3107,9 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="T38" s="1"/>
+      <c r="T38" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7312F42D-3569-41CE-97E9-3040550C6178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA13401-1DEB-4342-A90F-C568CE13CA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="186">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -625,6 +625,14 @@
   </si>
   <si>
     <t>HuangGai,HanDang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>node_31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의의 갈림길 5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1138,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1FA765-18DF-4AAD-91B0-AAB6166EA35D}">
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="8" bestFit="1" customWidth="1"/>
@@ -1512,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S39" si="1">S6+1</f>
+        <f t="shared" ref="S7:S40" si="1">S6+1</f>
         <v>3</v>
       </c>
       <c r="T7" s="1"/>
@@ -3153,7 +3161,53 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="T39" s="1"/>
+      <c r="T39" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1" t="str">
+        <f>VLOOKUP(C40,Overview!$B$2:$C$6,2,FALSE)</f>
+        <v>촉</v>
+      </c>
+      <c r="E40" s="1">
+        <v>200</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="N40" s="1">
+        <v>500</v>
+      </c>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1">
+        <v>1</v>
+      </c>
+      <c r="S40" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T40" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA13401-1DEB-4342-A90F-C568CE13CA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA60F183-FACF-4B71-BAA1-270AB96ACFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="S4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" s="1"/>
     </row>
@@ -1420,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="S5" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" s="1"/>
     </row>
@@ -1468,7 +1468,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1">
         <f>S5+1</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" s="1"/>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="S7" s="1">
         <f t="shared" ref="S7:S40" si="1">S6+1</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" s="1"/>
     </row>
@@ -1570,7 +1570,7 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T8" s="1"/>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="S9" s="1">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" s="1"/>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="S10" s="1">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T10" s="1"/>
     </row>
@@ -1727,7 +1727,7 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" s="1"/>
     </row>
@@ -1778,7 +1778,7 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" s="1"/>
     </row>
@@ -1829,7 +1829,7 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T13" s="1"/>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="S14" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" s="1"/>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T15" s="1"/>
     </row>
@@ -1985,7 +1985,7 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T16" s="1"/>
     </row>
@@ -2035,7 +2035,7 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T17" s="1"/>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T18" s="1"/>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="S19" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T19" s="1"/>
     </row>
@@ -2191,7 +2191,7 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T20" s="1"/>
     </row>
@@ -2244,7 +2244,7 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T21" s="1"/>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="S22" s="1">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>77</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="S23" s="1">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T23" s="1"/>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="S24" s="1">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T24" s="1"/>
     </row>
@@ -2457,7 +2457,7 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T25" s="1"/>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R26" s="1"/>
       <c r="S26" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T26" s="1"/>
     </row>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="S27" s="1">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T27" s="1"/>
     </row>
@@ -2613,7 +2613,7 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T28" s="1"/>
     </row>
@@ -2665,7 +2665,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T29" s="1"/>
     </row>
@@ -2718,7 +2718,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T30" s="1"/>
     </row>
@@ -2768,7 +2768,7 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T31" s="1"/>
     </row>
@@ -2820,7 +2820,7 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T32" s="1"/>
     </row>
@@ -2870,7 +2870,7 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T33" s="1"/>
     </row>
@@ -2922,7 +2922,7 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T34" s="1"/>
     </row>
@@ -2972,7 +2972,7 @@
       <c r="R35" s="1"/>
       <c r="S35" s="1">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T35" s="1"/>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="S36" s="1">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T36" s="1"/>
     </row>
@@ -3066,9 +3066,7 @@
       <c r="R37" s="1">
         <v>1</v>
       </c>
-      <c r="S37" s="1">
-        <v>1</v>
-      </c>
+      <c r="S37" s="1"/>
       <c r="T37" s="1" t="s">
         <v>79</v>
       </c>
@@ -3111,10 +3109,7 @@
       <c r="R38" s="1">
         <v>1</v>
       </c>
-      <c r="S38" s="1">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
+      <c r="S38" s="1"/>
       <c r="T38" s="1" t="s">
         <v>78</v>
       </c>
@@ -3157,10 +3152,7 @@
       <c r="R39" s="1">
         <v>1</v>
       </c>
-      <c r="S39" s="1">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
+      <c r="S39" s="1"/>
       <c r="T39" s="1" t="s">
         <v>184</v>
       </c>
@@ -3203,10 +3195,7 @@
       <c r="R40" s="1">
         <v>1</v>
       </c>
-      <c r="S40" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
+      <c r="S40" s="1"/>
       <c r="T40" s="1"/>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA60F183-FACF-4B71-BAA1-270AB96ACFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9208827E-E7A9-4B3D-A638-9C0564FEFFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -1520,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S40" si="1">S6+1</f>
+        <f t="shared" ref="S7:S36" si="1">S6+1</f>
         <v>5</v>
       </c>
       <c r="T7" s="1"/>
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" si="0"/>
@@ -1860,7 +1860,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" si="0"/>
@@ -2069,8 +2069,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
@@ -2122,7 +2121,7 @@
       </c>
       <c r="J19" s="1">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -2175,7 +2174,7 @@
       </c>
       <c r="J20" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -2226,7 +2225,7 @@
       </c>
       <c r="J21" s="1">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
@@ -2279,7 +2278,7 @@
       </c>
       <c r="J22" s="1">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1">
@@ -2336,7 +2335,7 @@
       </c>
       <c r="J23" s="1">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -2385,11 +2384,11 @@
         <v>5</v>
       </c>
       <c r="I24" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -2438,7 +2437,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" s="1">
         <v>9</v>
@@ -2488,10 +2487,10 @@
         <v>10</v>
       </c>
       <c r="I26" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
@@ -2541,11 +2540,11 @@
         <v>5</v>
       </c>
       <c r="I27" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" ref="J27:J34" si="3">J26+1</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -2597,7 +2596,7 @@
         <v>3</v>
       </c>
       <c r="J28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -2647,8 +2646,7 @@
         <v>3</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
@@ -2700,7 +2698,7 @@
       </c>
       <c r="J30" s="1">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
@@ -2752,7 +2750,7 @@
         <v>3</v>
       </c>
       <c r="J31" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -2802,8 +2800,7 @@
         <v>3</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
@@ -2854,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="J33" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2904,8 +2901,7 @@
         <v>3</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
@@ -2956,7 +2952,7 @@
         <v>3</v>
       </c>
       <c r="J35" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -3006,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="J36" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9208827E-E7A9-4B3D-A638-9C0564FEFFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228507DB-A8C2-4E7B-BFB7-83D09A9E954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -1319,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
@@ -1362,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -1405,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
@@ -2543,7 +2543,7 @@
         <v>2</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" ref="J27:J34" si="3">J26+1</f>
+        <f t="shared" ref="J27:J30" si="3">J26+1</f>
         <v>10</v>
       </c>
       <c r="K27" s="1"/>

--- a/ExcelToJSONConverter/excel/storyMode.xlsx
+++ b/ExcelToJSONConverter/excel/storyMode.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228507DB-A8C2-4E7B-BFB7-83D09A9E954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7617D4-186D-452E-AAAC-C282EA1271B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="StoryMode_Node" sheetId="6" r:id="rId2"/>
-    <sheet name="StoryMode_Unlock" sheetId="7" r:id="rId3"/>
-    <sheet name="StoryMode_Choice" sheetId="8" r:id="rId4"/>
+    <sheet name="s_story_node" sheetId="6" r:id="rId2"/>
+    <sheet name="s_story_node_unlock" sheetId="7" r:id="rId3"/>
+    <sheet name="s_story_node_choice" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
